--- a/project.xlsx
+++ b/project.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simran Jha\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2158D1D9-A3B5-4856-8556-58AE385FD7E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88973129-6012-49D3-883F-A682077628E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-97" yWindow="0" windowWidth="10510" windowHeight="10993" xr2:uid="{E09A6357-1891-442B-9721-2784400E97C9}"/>
+    <workbookView xWindow="-107" yWindow="-107" windowWidth="20847" windowHeight="11111" activeTab="1" xr2:uid="{E09A6357-1891-442B-9721-2784400E97C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>order_date</t>
   </si>
@@ -50,14 +51,39 @@
   <si>
     <t>fraud_flag</t>
   </si>
+  <si>
+    <t>Food Delivery Risk Dashboard</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Fraud</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Wastage %</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,9 +110,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -102,6 +129,3259 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Orders</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Over Time</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10980314960629919"/>
+          <c:y val="0.11615740740740743"/>
+          <c:w val="0.89019685039370078"/>
+          <c:h val="0.57734580052493434"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>total_orders</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$46</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>45292</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45293</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45294</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45295</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45296</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45297</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45298</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45299</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45300</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45301</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45302</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45303</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45304</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45305</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45306</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45307</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45308</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45309</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45310</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>45311</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>45312</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>45313</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>45314</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>45315</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>45316</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>45317</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>45318</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>45319</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>45320</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>45321</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>45322</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>45323</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>45324</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>45325</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>45326</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>45327</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>45328</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>45329</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>45330</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>45331</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>45332</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>45333</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>45334</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>45335</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45336</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>160</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C2D5-4A9F-9FE0-FFDDCA93FBA8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="986675040"/>
+        <c:axId val="986676960"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="986675040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="986676960"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="986676960"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="986675040"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Cancellations</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Trend</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>total_cancellations</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$46</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>45292</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45293</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45294</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45295</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45296</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45297</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45298</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45299</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45300</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45301</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45302</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45303</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45304</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45305</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45306</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45307</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45308</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45309</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45310</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>45311</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>45312</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>45313</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>45314</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>45315</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>45316</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>45317</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>45318</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>45319</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>45320</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>45321</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>45322</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>45323</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>45324</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>45325</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>45326</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>45327</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>45328</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>45329</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>45330</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>45331</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>45332</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>45333</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>45334</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>45335</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45336</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="45"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>18</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-63A5-4746-885B-0A4BF87FFF2E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1383771968"/>
+        <c:axId val="1383772448"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1383771968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1383772448"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1383772448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1383771968"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Fraud</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN" baseline="0"/>
+              <a:t> vs Normal Orders</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$48</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$49:$A$50</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Fraud</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Normal</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$49:$B$50</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>38</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C460-4E6A-8796-5233CC084E15}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="986680320"/>
+        <c:axId val="986694240"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="986680320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="986694240"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="986694240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="986680320"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>279778</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>61415</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>586854</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>81887</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA0F693D-2C6D-474E-9F5D-D83FF920482E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>388961</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>88711</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>491320</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>136478</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBC3C695-492F-4A8B-A5EF-C5FF2EDF04D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>354841</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>6824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>177420</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>75063</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D85A17B-5B13-49DC-A02E-C710F7423B26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -401,7 +3681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E7C03D-363C-4908-815F-45A7DB30F5B4}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.59765625" customWidth="1"/>
@@ -1193,7 +4473,63 @@
         <v>0</v>
       </c>
     </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49">
+        <f>COUNTIF(E2:E46,1)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50">
+        <f>COUNTIF(E2:E46,0)</f>
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F8AD4AF-EE55-4825-ABC5-48C5E0514CEC}">
+  <dimension ref="A1:A71"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="57.09765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="31.2" x14ac:dyDescent="0.65">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <f>AVERAGE(Sheet1!D2:D46)*100</f>
+        <v>42.222222222222221</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>